--- a/output/roomself_excel/1912.xlsx
+++ b/output/roomself_excel/1912.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>467930</v>
+        <v>136345</v>
       </c>
       <c r="D2" t="n">
-        <v>9616</v>
+        <v>3188</v>
       </c>
       <c r="E2" t="n">
-        <v>991</v>
+        <v>416</v>
       </c>
       <c r="F2" t="n">
-        <v>864</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>65750</v>
+        <v>255191</v>
       </c>
       <c r="D3" t="n">
-        <v>2052</v>
+        <v>4464</v>
       </c>
       <c r="E3" t="n">
-        <v>285</v>
+        <v>706</v>
       </c>
       <c r="F3" t="n">
-        <v>272</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>137532</v>
+        <v>65750</v>
       </c>
       <c r="D4" t="n">
-        <v>3008</v>
+        <v>2052</v>
       </c>
       <c r="E4" t="n">
-        <v>746</v>
+        <v>285</v>
       </c>
       <c r="F4" t="n">
-        <v>336</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>77504</v>
+        <v>137532</v>
       </c>
       <c r="D5" t="n">
-        <v>2280</v>
+        <v>3008</v>
       </c>
       <c r="E5" t="n">
-        <v>346</v>
+        <v>460</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6">
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90695</v>
+        <v>77504</v>
       </c>
       <c r="D6" t="n">
-        <v>2548</v>
+        <v>2280</v>
       </c>
       <c r="E6" t="n">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="F6" t="n">
         <v>22</v>
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>147693</v>
+        <v>90695</v>
       </c>
       <c r="D7" t="n">
-        <v>4804</v>
+        <v>2548</v>
       </c>
       <c r="E7" t="n">
-        <v>704</v>
+        <v>296</v>
       </c>
       <c r="F7" t="n">
-        <v>286</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57071</v>
+        <v>91357</v>
       </c>
       <c r="D8" t="n">
-        <v>1920</v>
+        <v>2540</v>
       </c>
       <c r="E8" t="n">
-        <v>453</v>
+        <v>317</v>
       </c>
       <c r="F8" t="n">
-        <v>150</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>91357</v>
+        <v>24684</v>
       </c>
       <c r="D11" t="n">
-        <v>2540</v>
+        <v>1376</v>
       </c>
       <c r="E11" t="n">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="F11" t="n">
-        <v>262</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24684</v>
+        <v>45980</v>
       </c>
       <c r="D12" t="n">
-        <v>1376</v>
+        <v>1728</v>
       </c>
       <c r="E12" t="n">
-        <v>264</v>
+        <v>190</v>
       </c>
       <c r="F12" t="n">
-        <v>124</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>45980</v>
+        <v>25920</v>
       </c>
       <c r="D13" t="n">
-        <v>1728</v>
+        <v>1308</v>
       </c>
       <c r="E13" t="n">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="F13" t="n">
         <v>22</v>
@@ -730,17 +730,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25920</v>
+        <v>147693</v>
       </c>
       <c r="D14" t="n">
-        <v>1308</v>
+        <v>4804</v>
       </c>
       <c r="E14" t="n">
-        <v>135</v>
+        <v>346</v>
       </c>
       <c r="F14" t="n">
         <v>22</v>
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20352</v>
+        <v>161</v>
       </c>
       <c r="D15" t="n">
-        <v>1192</v>
+        <v>120</v>
       </c>
       <c r="E15" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>161</v>
+        <v>89655</v>
       </c>
       <c r="D16" t="n">
-        <v>120</v>
+        <v>2528</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17">
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>89655</v>
+        <v>354692</v>
       </c>
       <c r="D17" t="n">
-        <v>2528</v>
+        <v>5684</v>
       </c>
       <c r="E17" t="n">
-        <v>439</v>
+        <v>1006</v>
       </c>
       <c r="F17" t="n">
-        <v>237</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>398922</v>
+        <v>356620</v>
       </c>
       <c r="D18" t="n">
-        <v>6621</v>
+        <v>5584</v>
       </c>
       <c r="E18" t="n">
-        <v>814</v>
+        <v>1154</v>
       </c>
       <c r="F18" t="n">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>354692</v>
+        <v>352448</v>
       </c>
       <c r="D19" t="n">
-        <v>5684</v>
+        <v>4829</v>
       </c>
       <c r="E19" t="n">
-        <v>1006</v>
+        <v>555</v>
       </c>
       <c r="F19" t="n">
-        <v>481</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,86 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>356620</v>
+        <v>57071</v>
       </c>
       <c r="D20" t="n">
-        <v>5584</v>
+        <v>1920</v>
       </c>
       <c r="E20" t="n">
-        <v>1154</v>
+        <v>217</v>
       </c>
       <c r="F20" t="n">
-        <v>456</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>76394</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3640</v>
+      </c>
+      <c r="E21" t="n">
+        <v>301</v>
+      </c>
+      <c r="F21" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>20352</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1192</v>
+      </c>
+      <c r="E22" t="n">
+        <v>214</v>
+      </c>
+      <c r="F22" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>46474</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1798</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/1912.xlsx
+++ b/output/roomself_excel/1912.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,11 +510,38 @@
       <c r="D2" t="n">
         <v>3188</v>
       </c>
-      <c r="E2" t="n">
-        <v>416</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>383</v>
+        <v>394</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>321</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>22</v>
+      </c>
+      <c r="M2" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +559,31 @@
       <c r="D3" t="n">
         <v>4464</v>
       </c>
-      <c r="E3" t="n">
-        <v>706</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>448</v>
-      </c>
+        <v>640</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>499</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +600,31 @@
       <c r="D4" t="n">
         <v>2052</v>
       </c>
-      <c r="E4" t="n">
-        <v>285</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>272</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="G4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>250</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +641,38 @@
       <c r="D5" t="n">
         <v>3008</v>
       </c>
-      <c r="E5" t="n">
-        <v>460</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>336</v>
+        <v>293</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>438</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>21</v>
+      </c>
+      <c r="M5" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +690,23 @@
       <c r="D6" t="n">
         <v>2280</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>346</v>
       </c>
-      <c r="F6" t="n">
-        <v>22</v>
-      </c>
+      <c r="G6" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +723,31 @@
       <c r="D7" t="n">
         <v>2548</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>296</v>
       </c>
-      <c r="F7" t="n">
-        <v>22</v>
-      </c>
+      <c r="G7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>292</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +764,38 @@
       <c r="D8" t="n">
         <v>2540</v>
       </c>
-      <c r="E8" t="n">
-        <v>317</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>262</v>
+        <v>296</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>22</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>296</v>
+      </c>
+      <c r="M8" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -629,12 +813,23 @@
       <c r="D9" t="n">
         <v>876</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="G9" t="n">
+        <v>58</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +846,15 @@
       <c r="D10" t="n">
         <v>1000</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +871,31 @@
       <c r="D11" t="n">
         <v>1376</v>
       </c>
-      <c r="E11" t="n">
-        <v>264</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>124</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="G11" t="n">
+        <v>22</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>102</v>
+      </c>
+      <c r="J11" t="n">
+        <v>22</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +912,23 @@
       <c r="D12" t="n">
         <v>1728</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>190</v>
       </c>
-      <c r="F12" t="n">
-        <v>22</v>
-      </c>
+      <c r="G12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +945,31 @@
       <c r="D13" t="n">
         <v>1308</v>
       </c>
-      <c r="E13" t="n">
-        <v>135</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
         <v>22</v>
       </c>
+      <c r="G13" t="n">
+        <v>21</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>113</v>
+      </c>
+      <c r="J13" t="n">
+        <v>22</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +986,23 @@
       <c r="D14" t="n">
         <v>4804</v>
       </c>
-      <c r="E14" t="n">
-        <v>346</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="G14" t="n">
+        <v>22</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1019,15 @@
       <c r="D15" t="n">
         <v>120</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1044,31 @@
       <c r="D16" t="n">
         <v>2528</v>
       </c>
-      <c r="E16" t="n">
-        <v>439</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>237</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="G16" t="n">
+        <v>22</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>417</v>
+      </c>
+      <c r="J16" t="n">
+        <v>22</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1085,31 @@
       <c r="D17" t="n">
         <v>5684</v>
       </c>
-      <c r="E17" t="n">
-        <v>1006</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>481</v>
-      </c>
+        <v>918</v>
+      </c>
+      <c r="G17" t="n">
+        <v>22</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>788</v>
+      </c>
+      <c r="J17" t="n">
+        <v>22</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1126,31 @@
       <c r="D18" t="n">
         <v>5584</v>
       </c>
-      <c r="E18" t="n">
-        <v>1154</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>456</v>
-      </c>
+        <v>760</v>
+      </c>
+      <c r="G18" t="n">
+        <v>22</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>962</v>
+      </c>
+      <c r="J18" t="n">
+        <v>22</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1167,23 @@
       <c r="D19" t="n">
         <v>4829</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>555</v>
       </c>
-      <c r="F19" t="n">
-        <v>22</v>
-      </c>
+      <c r="G19" t="n">
+        <v>22</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1200,23 @@
       <c r="D20" t="n">
         <v>1920</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>217</v>
       </c>
-      <c r="F20" t="n">
-        <v>22</v>
-      </c>
+      <c r="G20" t="n">
+        <v>22</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1233,23 @@
       <c r="D21" t="n">
         <v>3640</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>301</v>
       </c>
-      <c r="F21" t="n">
-        <v>261</v>
-      </c>
+      <c r="G21" t="n">
+        <v>22</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1266,31 @@
       <c r="D22" t="n">
         <v>1192</v>
       </c>
-      <c r="E22" t="n">
-        <v>214</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>128</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="G22" t="n">
+        <v>22</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>106</v>
+      </c>
+      <c r="J22" t="n">
+        <v>22</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1307,15 @@
       <c r="D23" t="n">
         <v>1798</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
